--- a/survey_templates/034_net_promoter_score_nps_survey--survey_templates.xlsx
+++ b/survey_templates/034_net_promoter_score_nps_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_very_likely</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Not very likely</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -892,29 +892,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>definitely_likely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Very likely</t>
+          <t>Definitely likely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>will_recommend_choices</t>
+          <t>will_recommend_business_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>definitely_likely</t>
+          <t>very_unlikely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Definitely likely</t>
+          <t>Very unlikely</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>very_unlikely</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Very unlikely</t>
+          <t>Not very likely</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_very_likely</t>
+          <t>somewhat_unlikely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not very likely</t>
+          <t>Somewhat unlikely</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>somewhat_unlikely</t>
+          <t>neither_likely_nor_unlikely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Somewhat unlikely</t>
+          <t>Neither likely nor unlikely</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>neither_likely_nor_unlikely</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Neither likely nor unlikely</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Somewhat likely</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1011,44 +1011,10 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_very_likely</t>
+          <t>definitely_likely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>Not very likely</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>will_recommend_business_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>very_likely</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Very likely</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>will_recommend_business_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>definitely_likely</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Definitely likely</t>
         </is>
